--- a/output/semanal/01_perfil_semanal.xlsx
+++ b/output/semanal/01_perfil_semanal.xlsx
@@ -22,13 +22,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -47,12 +50,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -423,12 +435,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>metrica</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -503,27 +515,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>nulos</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ceros_pct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>valores_unicos</t>
         </is>
@@ -670,10 +682,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2359550561797753</v>
+        <v>0.4550561797752809</v>
       </c>
       <c r="E8" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9">
@@ -712,10 +724,10 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2078651685393259</v>
+        <v>0.4044943820224719</v>
       </c>
       <c r="E10" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -754,10 +766,10 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1853932584269663</v>
+        <v>0.3595505617977528</v>
       </c>
       <c r="E12" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -1135,7 +1147,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31">
@@ -1366,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42">
@@ -1720,19 +1732,19 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>semana_inicio</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>target_compras_importe_semanal</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44928</v>
       </c>
       <c r="B2" t="n">
@@ -1740,7 +1752,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44935</v>
       </c>
       <c r="B3" t="n">
@@ -1748,7 +1760,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44942</v>
       </c>
       <c r="B4" t="n">
@@ -1756,7 +1768,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44949</v>
       </c>
       <c r="B5" t="n">
@@ -1764,7 +1776,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44956</v>
       </c>
       <c r="B6" t="n">
@@ -1772,7 +1784,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44963</v>
       </c>
       <c r="B7" t="n">
@@ -1780,7 +1792,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44970</v>
       </c>
       <c r="B8" t="n">
@@ -1788,7 +1800,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44977</v>
       </c>
       <c r="B9" t="n">
@@ -1796,7 +1808,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="B10" t="n">
@@ -1804,7 +1816,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44991</v>
       </c>
       <c r="B11" t="n">
@@ -1812,7 +1824,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44998</v>
       </c>
       <c r="B12" t="n">
@@ -1820,7 +1832,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45005</v>
       </c>
       <c r="B13" t="n">
@@ -1828,7 +1840,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45012</v>
       </c>
       <c r="B14" t="n">
@@ -1836,7 +1848,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45019</v>
       </c>
       <c r="B15" t="n">
@@ -1844,7 +1856,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45026</v>
       </c>
       <c r="B16" t="n">
@@ -1852,7 +1864,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45033</v>
       </c>
       <c r="B17" t="n">
@@ -1860,7 +1872,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45040</v>
       </c>
       <c r="B18" t="n">
@@ -1868,7 +1880,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B19" t="n">
@@ -1876,7 +1888,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45054</v>
       </c>
       <c r="B20" t="n">
@@ -1884,7 +1896,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45061</v>
       </c>
       <c r="B21" t="n">
@@ -1892,7 +1904,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45068</v>
       </c>
       <c r="B22" t="n">
@@ -1900,7 +1912,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>45075</v>
       </c>
       <c r="B23" t="n">
@@ -1908,7 +1920,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>45082</v>
       </c>
       <c r="B24" t="n">
@@ -1916,7 +1928,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>45089</v>
       </c>
       <c r="B25" t="n">
@@ -1924,7 +1936,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>45096</v>
       </c>
       <c r="B26" t="n">
@@ -1932,7 +1944,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>45103</v>
       </c>
       <c r="B27" t="n">
@@ -1940,7 +1952,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>45110</v>
       </c>
       <c r="B28" t="n">
@@ -1948,7 +1960,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>45117</v>
       </c>
       <c r="B29" t="n">
@@ -1956,7 +1968,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>45124</v>
       </c>
       <c r="B30" t="n">
@@ -1964,7 +1976,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>45131</v>
       </c>
       <c r="B31" t="n">
@@ -1972,7 +1984,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B32" t="n">
@@ -1980,7 +1992,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>45145</v>
       </c>
       <c r="B33" t="n">
@@ -1988,7 +2000,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>45152</v>
       </c>
       <c r="B34" t="n">
@@ -1996,7 +2008,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>45159</v>
       </c>
       <c r="B35" t="n">
@@ -2004,7 +2016,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>45166</v>
       </c>
       <c r="B36" t="n">
@@ -2012,7 +2024,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>45173</v>
       </c>
       <c r="B37" t="n">
@@ -2020,7 +2032,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>45180</v>
       </c>
       <c r="B38" t="n">
@@ -2028,7 +2040,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>45187</v>
       </c>
       <c r="B39" t="n">
@@ -2036,7 +2048,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>45194</v>
       </c>
       <c r="B40" t="n">
@@ -2044,7 +2056,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>45201</v>
       </c>
       <c r="B41" t="n">
@@ -2052,7 +2064,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>45208</v>
       </c>
       <c r="B42" t="n">
@@ -2060,7 +2072,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>45215</v>
       </c>
       <c r="B43" t="n">
@@ -2068,7 +2080,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>45222</v>
       </c>
       <c r="B44" t="n">
@@ -2076,7 +2088,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45229</v>
       </c>
       <c r="B45" t="n">
@@ -2084,7 +2096,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45236</v>
       </c>
       <c r="B46" t="n">
@@ -2092,7 +2104,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45243</v>
       </c>
       <c r="B47" t="n">
@@ -2100,7 +2112,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45250</v>
       </c>
       <c r="B48" t="n">
@@ -2108,7 +2120,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45257</v>
       </c>
       <c r="B49" t="n">
@@ -2116,7 +2128,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45264</v>
       </c>
       <c r="B50" t="n">
@@ -2124,7 +2136,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45271</v>
       </c>
       <c r="B51" t="n">
@@ -2132,7 +2144,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45278</v>
       </c>
       <c r="B52" t="n">
@@ -2140,7 +2152,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45285</v>
       </c>
       <c r="B53" t="n">
@@ -2148,7 +2160,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B54" t="n">
@@ -2156,7 +2168,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45299</v>
       </c>
       <c r="B55" t="n">
@@ -2164,7 +2176,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45306</v>
       </c>
       <c r="B56" t="n">
@@ -2172,7 +2184,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45313</v>
       </c>
       <c r="B57" t="n">
@@ -2180,7 +2192,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45320</v>
       </c>
       <c r="B58" t="n">
@@ -2188,7 +2200,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45327</v>
       </c>
       <c r="B59" t="n">
@@ -2196,7 +2208,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45334</v>
       </c>
       <c r="B60" t="n">
@@ -2204,7 +2216,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45341</v>
       </c>
       <c r="B61" t="n">
@@ -2212,7 +2224,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45348</v>
       </c>
       <c r="B62" t="n">
@@ -2220,7 +2232,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45355</v>
       </c>
       <c r="B63" t="n">
@@ -2228,7 +2240,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45362</v>
       </c>
       <c r="B64" t="n">
@@ -2236,7 +2248,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45369</v>
       </c>
       <c r="B65" t="n">
@@ -2244,7 +2256,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45376</v>
       </c>
       <c r="B66" t="n">
@@ -2252,7 +2264,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B67" t="n">
@@ -2260,7 +2272,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45390</v>
       </c>
       <c r="B68" t="n">
@@ -2268,7 +2280,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45397</v>
       </c>
       <c r="B69" t="n">
@@ -2276,7 +2288,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45404</v>
       </c>
       <c r="B70" t="n">
@@ -2284,7 +2296,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45411</v>
       </c>
       <c r="B71" t="n">
@@ -2292,7 +2304,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45418</v>
       </c>
       <c r="B72" t="n">
@@ -2300,7 +2312,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45425</v>
       </c>
       <c r="B73" t="n">
@@ -2308,7 +2320,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>45432</v>
       </c>
       <c r="B74" t="n">
@@ -2316,7 +2328,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>45439</v>
       </c>
       <c r="B75" t="n">
@@ -2324,7 +2336,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>45446</v>
       </c>
       <c r="B76" t="n">
@@ -2332,7 +2344,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>45453</v>
       </c>
       <c r="B77" t="n">
@@ -2340,7 +2352,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>45460</v>
       </c>
       <c r="B78" t="n">
@@ -2348,7 +2360,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>45467</v>
       </c>
       <c r="B79" t="n">
@@ -2356,7 +2368,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B80" t="n">
@@ -2364,7 +2376,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>45481</v>
       </c>
       <c r="B81" t="n">
@@ -2372,7 +2384,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>45488</v>
       </c>
       <c r="B82" t="n">
@@ -2380,7 +2392,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>45495</v>
       </c>
       <c r="B83" t="n">
@@ -2388,7 +2400,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>45502</v>
       </c>
       <c r="B84" t="n">
@@ -2396,7 +2408,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="B85" t="n">
@@ -2404,7 +2416,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>45516</v>
       </c>
       <c r="B86" t="n">
@@ -2412,7 +2424,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>45523</v>
       </c>
       <c r="B87" t="n">
@@ -2420,7 +2432,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>45530</v>
       </c>
       <c r="B88" t="n">
@@ -2428,7 +2440,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>45537</v>
       </c>
       <c r="B89" t="n">
@@ -2436,7 +2448,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>45544</v>
       </c>
       <c r="B90" t="n">
@@ -2444,7 +2456,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>45551</v>
       </c>
       <c r="B91" t="n">
@@ -2452,7 +2464,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>45558</v>
       </c>
       <c r="B92" t="n">
@@ -2460,7 +2472,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B93" t="n">
@@ -2468,7 +2480,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>45572</v>
       </c>
       <c r="B94" t="n">
@@ -2476,7 +2488,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>45579</v>
       </c>
       <c r="B95" t="n">
@@ -2484,7 +2496,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B96" t="n">
@@ -2492,7 +2504,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>45593</v>
       </c>
       <c r="B97" t="n">
@@ -2500,7 +2512,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>45600</v>
       </c>
       <c r="B98" t="n">
@@ -2508,7 +2520,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>45607</v>
       </c>
       <c r="B99" t="n">
@@ -2516,7 +2528,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>45614</v>
       </c>
       <c r="B100" t="n">
@@ -2524,7 +2536,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>45621</v>
       </c>
       <c r="B101" t="n">
@@ -2532,7 +2544,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>45628</v>
       </c>
       <c r="B102" t="n">
@@ -2540,7 +2552,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>45635</v>
       </c>
       <c r="B103" t="n">
@@ -2548,7 +2560,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>45642</v>
       </c>
       <c r="B104" t="n">
@@ -2556,7 +2568,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>45649</v>
       </c>
       <c r="B105" t="n">
@@ -2564,7 +2576,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>45656</v>
       </c>
       <c r="B106" t="n">
@@ -2572,7 +2584,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>45663</v>
       </c>
       <c r="B107" t="n">
@@ -2580,7 +2592,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>45670</v>
       </c>
       <c r="B108" t="n">
@@ -2588,7 +2600,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>45677</v>
       </c>
       <c r="B109" t="n">
@@ -2596,7 +2608,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>45684</v>
       </c>
       <c r="B110" t="n">
@@ -2604,7 +2616,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>45691</v>
       </c>
       <c r="B111" t="n">
@@ -2612,7 +2624,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>45698</v>
       </c>
       <c r="B112" t="n">
@@ -2620,7 +2632,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>45705</v>
       </c>
       <c r="B113" t="n">
@@ -2628,7 +2640,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>45712</v>
       </c>
       <c r="B114" t="n">
@@ -2636,7 +2648,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>45719</v>
       </c>
       <c r="B115" t="n">
@@ -2644,7 +2656,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>45726</v>
       </c>
       <c r="B116" t="n">
@@ -2652,7 +2664,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>45733</v>
       </c>
       <c r="B117" t="n">
@@ -2660,7 +2672,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>45740</v>
       </c>
       <c r="B118" t="n">
@@ -2668,7 +2680,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B119" t="n">
@@ -2676,7 +2688,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>45754</v>
       </c>
       <c r="B120" t="n">
@@ -2684,7 +2696,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>45761</v>
       </c>
       <c r="B121" t="n">
@@ -2692,7 +2704,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>45768</v>
       </c>
       <c r="B122" t="n">
@@ -2700,7 +2712,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>45775</v>
       </c>
       <c r="B123" t="n">
@@ -2708,7 +2720,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>45782</v>
       </c>
       <c r="B124" t="n">
@@ -2716,7 +2728,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>45789</v>
       </c>
       <c r="B125" t="n">
@@ -2724,7 +2736,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>45796</v>
       </c>
       <c r="B126" t="n">
@@ -2732,7 +2744,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>45803</v>
       </c>
       <c r="B127" t="n">
@@ -2740,7 +2752,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>45810</v>
       </c>
       <c r="B128" t="n">
@@ -2748,7 +2760,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>45817</v>
       </c>
       <c r="B129" t="n">
@@ -2756,7 +2768,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>45824</v>
       </c>
       <c r="B130" t="n">
@@ -2764,7 +2776,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="B131" t="n">
@@ -2772,7 +2784,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B132" t="n">
@@ -2780,7 +2792,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>45845</v>
       </c>
       <c r="B133" t="n">
@@ -2788,7 +2800,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>45852</v>
       </c>
       <c r="B134" t="n">
@@ -2796,7 +2808,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>45859</v>
       </c>
       <c r="B135" t="n">
@@ -2804,7 +2816,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>45866</v>
       </c>
       <c r="B136" t="n">
@@ -2812,7 +2824,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>45873</v>
       </c>
       <c r="B137" t="n">
@@ -2820,7 +2832,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>45880</v>
       </c>
       <c r="B138" t="n">
@@ -2828,7 +2840,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>45887</v>
       </c>
       <c r="B139" t="n">
@@ -2836,7 +2848,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>45894</v>
       </c>
       <c r="B140" t="n">
@@ -2844,7 +2856,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B141" t="n">
@@ -2852,7 +2864,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>45908</v>
       </c>
       <c r="B142" t="n">
@@ -2860,7 +2872,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>45915</v>
       </c>
       <c r="B143" t="n">
@@ -2868,7 +2880,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>45922</v>
       </c>
       <c r="B144" t="n">
@@ -2876,7 +2888,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>45929</v>
       </c>
       <c r="B145" t="n">
@@ -2884,7 +2896,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>45936</v>
       </c>
       <c r="B146" t="n">
@@ -2892,7 +2904,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>45943</v>
       </c>
       <c r="B147" t="n">
@@ -2900,7 +2912,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>45950</v>
       </c>
       <c r="B148" t="n">
@@ -2908,7 +2920,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>45957</v>
       </c>
       <c r="B149" t="n">
@@ -2916,7 +2928,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="B150" t="n">
@@ -2924,7 +2936,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>45971</v>
       </c>
       <c r="B151" t="n">
@@ -2932,7 +2944,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>45978</v>
       </c>
       <c r="B152" t="n">
@@ -2940,7 +2952,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>45985</v>
       </c>
       <c r="B153" t="n">
@@ -2948,7 +2960,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B154" t="n">
@@ -2956,7 +2968,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45999</v>
       </c>
       <c r="B155" t="n">
@@ -2964,7 +2976,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>46006</v>
       </c>
       <c r="B156" t="n">
@@ -2972,7 +2984,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>46013</v>
       </c>
       <c r="B157" t="n">
@@ -2980,7 +2992,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>46020</v>
       </c>
       <c r="B158" t="n">
@@ -2988,7 +3000,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>46027</v>
       </c>
       <c r="B159" t="n">
@@ -2996,7 +3008,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>46034</v>
       </c>
       <c r="B160" t="n">
@@ -3004,7 +3016,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>46041</v>
       </c>
       <c r="B161" t="n">
@@ -3012,7 +3024,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>46048</v>
       </c>
       <c r="B162" t="n">
@@ -3020,7 +3032,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>46055</v>
       </c>
       <c r="B163" t="n">
@@ -3028,7 +3040,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>46062</v>
       </c>
       <c r="B164" t="n">
@@ -3036,7 +3048,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>46069</v>
       </c>
       <c r="B165" t="n">
@@ -3044,7 +3056,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>46076</v>
       </c>
       <c r="B166" t="n">
@@ -3052,7 +3064,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>46083</v>
       </c>
       <c r="B167" t="n">
@@ -3060,7 +3072,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>46090</v>
       </c>
       <c r="B168" t="n">
@@ -3068,7 +3080,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="B169" t="n">
@@ -3076,7 +3088,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>46104</v>
       </c>
       <c r="B170" t="n">
@@ -3084,7 +3096,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>46111</v>
       </c>
       <c r="B171" t="n">
@@ -3092,7 +3104,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>46118</v>
       </c>
       <c r="B172" t="n">
@@ -3100,7 +3112,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>46125</v>
       </c>
       <c r="B173" t="n">
@@ -3108,7 +3120,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>46132</v>
       </c>
       <c r="B174" t="n">
@@ -3116,7 +3128,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="B175" t="n">
@@ -3124,7 +3136,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="B176" t="n">
@@ -3132,7 +3144,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="B177" t="n">
@@ -3140,7 +3152,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B178" t="n">
@@ -3148,7 +3160,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>46167</v>
       </c>
       <c r="B179" t="n">

--- a/output/semanal/01_perfil_semanal.xlsx
+++ b/output/semanal/01_perfil_semanal.xlsx
@@ -1561,7 +1561,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>exog_nacimientos_indice_semanal</t>
+          <t>exog_semana_anio_sin</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1576,13 +1576,13 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>exog_semana_anio_sin</t>
+          <t>exog_semana_anio_cos</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1597,13 +1597,13 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>exog_semana_anio_cos</t>
+          <t>exog_mes_sin</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1618,13 +1618,13 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>exog_mes_sin</t>
+          <t>exog_mes_cos</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1645,7 +1645,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>exog_mes_cos</t>
+          <t>exog_nacimientos_indice_publicado_lag_1s</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1660,13 +1660,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>exog_inpc_publicado</t>
+          <t>exog_inpc_publicado_lag_1s</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1687,7 +1687,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>exog_temperatura_lag_1s</t>
+          <t>exog_temperatura_publicado_lag_1s</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
